--- a/test_data/data_merge_testdata_2.xlsx
+++ b/test_data/data_merge_testdata_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git clone projects\Data-Merge-Utility-DMU-\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E8A8BE-A958-48D6-B250-4539AD573020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F4365B-7B63-4E4D-A7EC-8B0C5B52F51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,6 +76,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -112,9 +115,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -398,7 +402,7 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -423,8 +427,8 @@
       <c r="A2">
         <v>4</v>
       </c>
-      <c r="B2" s="1">
-        <v>45815</v>
+      <c r="B2" s="2">
+        <v>46180</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
